--- a/Luban/Datas/EnemyDrop.xlsx
+++ b/Luban/Datas/EnemyDrop.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
@@ -2350,31 +2350,60 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="n">
+      <c r="B60" s="0" t="n">
         <v>57</v>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="0" t="inlineStr">
         <is>
           <t>enemy_drop_enemy_resource_01</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="E60" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" t="inlineStr">
+      <c r="E60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="0" t="inlineStr">
         <is>
           <t>star</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>2</v>
-      </c>
-      <c r="H60" t="b">
+      <c r="G60" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>enemy_drop_level1_resource_helicopter_hp</t>
+        </is>
+      </c>
+      <c r="D61" s="0" t="inlineStr">
+        <is>
+          <t>level1_resource_helicopter</t>
+        </is>
+      </c>
+      <c r="E61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="0" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="G61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="0" t="b">
         <v>0</v>
       </c>
     </row>
